--- a/artfynd/A 21266-2022 artfynd.xlsx
+++ b/artfynd/A 21266-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135946023</v>
       </c>
       <c r="B2" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21266-2022 artfynd.xlsx
+++ b/artfynd/A 21266-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135946023</v>
       </c>
       <c r="B2" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21266-2022 artfynd.xlsx
+++ b/artfynd/A 21266-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135946023</v>
       </c>
       <c r="B2" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21266-2022 artfynd.xlsx
+++ b/artfynd/A 21266-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135946023</v>
       </c>
       <c r="B2" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21266-2022 artfynd.xlsx
+++ b/artfynd/A 21266-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135946023</v>
       </c>
       <c r="B2" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21266-2022 artfynd.xlsx
+++ b/artfynd/A 21266-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135946023</v>
       </c>
       <c r="B2" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
